--- a/internal_doc/14.性能分析/sequoiadb_perf.xlsx
+++ b/internal_doc/14.性能分析/sequoiadb_perf.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="standalone" sheetId="1" r:id="rId1"/>
+    <sheet name="2015-6-11" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="444">
   <si>
     <t>debug</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1332,6 +1333,41 @@
   </si>
   <si>
     <t>96.812875s</t>
+  </si>
+  <si>
+    <t>1500w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int_idx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_idx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15000w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>release r19173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mode:
+0 - 原有流程
+1 - 使用rtnSorting排序的流程对key排序
+2 - 只在内存对ixmKey排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1371,7 +1407,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1379,13 +1415,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3435,4 +3504,159 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:F12"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="4" max="4" width="13.375" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="63" customHeight="1">
+      <c r="C1" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" ht="21.75" customHeight="1"/>
+    <row r="3" spans="2:6" ht="24" customHeight="1">
+      <c r="B3" s="3"/>
+      <c r="C3" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="23.25" customHeight="1">
+      <c r="B4" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>106.265862</v>
+      </c>
+      <c r="E4" s="3">
+        <v>425.74435599999998</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="21" customHeight="1">
+      <c r="B5" s="4"/>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>122.36233</v>
+      </c>
+      <c r="E5" s="3">
+        <v>148.344741</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="22.5" customHeight="1">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>66.724609000000001</v>
+      </c>
+      <c r="E6" s="3">
+        <v>104.950185</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="27" customHeight="1">
+      <c r="B7" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>460.51916999999997</v>
+      </c>
+      <c r="E7" s="3">
+        <v>6097.289941</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="29.25" customHeight="1">
+      <c r="B8" s="4"/>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>445.52569999999997</v>
+      </c>
+      <c r="E8" s="3">
+        <v>595.301424</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="31.5" customHeight="1">
+      <c r="B9" s="4"/>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>256.28217000000001</v>
+      </c>
+      <c r="E9" s="3">
+        <v>397.94641100000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="27.75" customHeight="1">
+      <c r="B10" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1055.3175799999999</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="2:6" ht="27.75" customHeight="1">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1615.814895</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1785.6127730000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="31.5" customHeight="1">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>815.15718000000004</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1881.2179470000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B12"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/14.性能分析/sequoiadb_perf.xlsx
+++ b/internal_doc/14.性能分析/sequoiadb_perf.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="447">
   <si>
     <t>debug</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1367,6 +1367,18 @@
 0 - 原有流程
 1 - 使用rtnSorting排序的流程对key排序
 2 - 只在内存对ixmKey排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>online</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offline</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmsIndexBuilder</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1434,16 +1446,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1454,6 +1463,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3508,24 +3526,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:F12"/>
+  <dimension ref="B1:H12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="13.375" customWidth="1"/>
     <col min="5" max="5" width="12.75" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
+    <col min="8" max="8" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="63" customHeight="1">
-      <c r="C1" s="6" t="s">
+    <row r="1" spans="2:8" ht="63" customHeight="1">
+      <c r="C1" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="21.75" customHeight="1"/>
-    <row r="3" spans="2:6" ht="24" customHeight="1">
+    <row r="2" spans="2:8" ht="21.75" customHeight="1"/>
+    <row r="3" spans="2:8" ht="24" customHeight="1">
       <c r="B3" s="3"/>
       <c r="C3" s="2" t="s">
         <v>439</v>
@@ -3536,9 +3556,15 @@
       <c r="E3" s="2" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" ht="23.25" customHeight="1">
-      <c r="B4" s="4" t="s">
+      <c r="G3" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="23.25" customHeight="1">
+      <c r="B4" s="8" t="s">
         <v>436</v>
       </c>
       <c r="C4" s="3">
@@ -3550,9 +3576,15 @@
       <c r="E4" s="3">
         <v>425.74435599999998</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" ht="21" customHeight="1">
-      <c r="B5" s="4"/>
+      <c r="G4" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H4" s="4">
+        <v>402.40289300000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="21" customHeight="1">
+      <c r="B5" s="8"/>
       <c r="C5" s="3">
         <v>1</v>
       </c>
@@ -3562,9 +3594,15 @@
       <c r="E5" s="3">
         <v>148.344741</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B6" s="4"/>
+      <c r="G5" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="H5" s="4">
+        <v>131.39678900000001</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="22.5" customHeight="1">
+      <c r="B6" s="8"/>
       <c r="C6" s="3">
         <v>2</v>
       </c>
@@ -3575,8 +3613,8 @@
         <v>104.950185</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="27" customHeight="1">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="2:8" ht="27" customHeight="1">
+      <c r="B7" s="8" t="s">
         <v>440</v>
       </c>
       <c r="C7" s="3">
@@ -3589,8 +3627,8 @@
         <v>6097.289941</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B8" s="4"/>
+    <row r="8" spans="2:8" ht="29.25" customHeight="1">
+      <c r="B8" s="8"/>
       <c r="C8" s="3">
         <v>1</v>
       </c>
@@ -3601,8 +3639,8 @@
         <v>595.301424</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B9" s="4"/>
+    <row r="9" spans="2:8" ht="31.5" customHeight="1">
+      <c r="B9" s="8"/>
       <c r="C9" s="3">
         <v>2</v>
       </c>
@@ -3613,11 +3651,11 @@
         <v>397.94641100000001</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="2:8" ht="27.75" customHeight="1">
+      <c r="B10" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10" s="3">
@@ -3625,9 +3663,9 @@
       </c>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B11" s="4"/>
-      <c r="C11" s="5">
+    <row r="11" spans="2:8" ht="27.75" customHeight="1">
+      <c r="B11" s="8"/>
+      <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="3">
@@ -3637,9 +3675,9 @@
         <v>1785.6127730000001</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B12" s="4"/>
-      <c r="C12" s="5">
+    <row r="12" spans="2:8" ht="31.5" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="4">
         <v>2</v>
       </c>
       <c r="D12" s="3">
